--- a/slides/uet-oop-midterm-practice-INT2204-80.xlsx
+++ b/slides/uet-oop-midterm-practice-INT2204-80.xlsx
@@ -848,7 +848,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>C1.1</t>
@@ -872,17 +871,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -895,7 +888,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>C1.2</t>
@@ -919,17 +911,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -942,7 +928,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>C1.3</t>
@@ -966,17 +951,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -989,7 +968,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>C1.4</t>
@@ -1013,17 +991,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -1036,7 +1008,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>C1.5</t>
@@ -1060,17 +1031,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1083,7 +1048,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>C1.6</t>
@@ -1107,17 +1071,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1130,7 +1088,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>C1.7</t>
@@ -1154,17 +1111,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1177,7 +1128,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>C1.8</t>
@@ -1201,17 +1151,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1224,7 +1168,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>C1.9</t>
@@ -1248,17 +1191,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -1271,7 +1208,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>C1.10</t>
@@ -1295,17 +1231,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -1318,7 +1248,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>C1.11</t>
@@ -1342,17 +1271,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -1365,7 +1288,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>C1.12</t>
@@ -1389,17 +1311,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1412,7 +1328,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>C1.13</t>
@@ -1436,17 +1351,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1459,7 +1368,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>C1.14</t>
@@ -1483,17 +1391,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -1506,7 +1408,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>C1.15</t>
@@ -1530,17 +1431,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -1553,7 +1448,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>C1.16</t>
@@ -1577,17 +1471,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -1600,7 +1488,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>C1.17</t>
@@ -1624,17 +1511,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -1647,7 +1528,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>C1.18</t>
@@ -1671,17 +1551,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -1694,7 +1568,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>C1.19</t>
@@ -1718,17 +1591,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -1741,7 +1608,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>C1.20</t>
@@ -1765,17 +1631,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -1788,7 +1648,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>C1.21</t>
@@ -1812,17 +1671,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -1835,7 +1688,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>C1.22</t>
@@ -1859,17 +1711,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -1882,7 +1728,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>C1.23</t>
@@ -1906,17 +1751,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -1929,7 +1768,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>C1.24</t>
@@ -1953,17 +1791,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Sai</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -1976,7 +1808,6 @@
           <t>Câu 1 - Đúng/Sai (5 điểm)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>C1.25</t>
@@ -2000,17 +1831,11 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Đúng</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -2023,7 +1848,6 @@
           <t>Câu 2 - Tự luận (1,5 điểm)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>C2.a</t>
@@ -2047,11 +1871,6 @@
           <t>llm_assisted</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Liên kết tĩnh xảy ra ở compile-time dựa trên kiểu tham chiếu (áp dụng cho phương thức static, private, final và overloading). Liên kết động xảy ra ở runtime dựa trên đối tượng thực tế trong Heap (áp dụng cho instance method bị overriding). Ví dụ minh họa gọi static method (static binding) và instance method override (dynamic binding).</t>
@@ -2074,7 +1893,6 @@
           <t>Câu 2 - Tự luận (1,5 điểm)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>C2.b</t>
@@ -2098,11 +1916,6 @@
           <t>llm_assisted</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Checked Exception: kế thừa Exception (trừ RuntimeException), bắt buộc try-catch hoặc throws ở compile-time (ví dụ IOException, SQLException). Unchecked Exception: kế thừa RuntimeException, không bắt buộc khai báo/bắt ở compile-time (ví dụ NullPointerException, ArithmeticException). Lý do: Checked buộc xử lý các lỗi ngoài tầm kiểm soát môi trường/tài nguyên; Unchecked cảnh báo lỗi logic lập trình cần sửa mã nguồn.</t>
@@ -2125,7 +1938,6 @@
           <t>Câu 3 - Một lựa chọn (2 điểm)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>C3.1</t>
@@ -2178,8 +1990,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -2192,7 +2002,6 @@
           <t>Câu 3 - Một lựa chọn (2 điểm)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>C3.2</t>
@@ -2242,8 +2051,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -2256,7 +2063,6 @@
           <t>Câu 3 - Một lựa chọn (2 điểm)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>C3.3</t>
@@ -2305,8 +2111,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" t="inlineStr">
@@ -2319,7 +2123,6 @@
           <t>Câu 3 - Một lựa chọn (2 điểm)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>C3.4</t>
@@ -2372,8 +2175,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -2386,7 +2187,6 @@
           <t>Câu 3 - Một lựa chọn (2 điểm)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>C3.5</t>
@@ -2437,8 +2237,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34" ht="220" customHeight="1">
       <c r="A34" t="inlineStr">
@@ -2453,21 +2251,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>class Account {
+          <t>abstract class Account {
     private String accountNumber;
     protected double balance;
     public Account(String accNum, double initialBalance) {
         accountNumber = accNum;
         balance = initialBalance;
     }
-    public void deposit(double amount) {
+    public abstract void processMonthlyFee();
+    Public void deposit(double amount) {
         balance += amount;
-    }
-    public void withdraw(double amount) throws Exception {
-        if (amount &gt; balance) {
-            throw new Exception("Insufficient balance");
-        }
-        balance -= amount;
     }
     public void printInfo() {
         System.out.println("Acc: " + accountNumber + ", Balance: " + balance);
@@ -2475,28 +2268,21 @@
 }
 public class SavingAccount extends Account {
     private double interestRate;
+    public SavingAccount(double rate) {
+        interestRate = rate;
+        super("SA_DEF", 100.0);
+    }
     public SavingAccount(String accNum, double initialBalance, double rate) {
         balance = initialBalance;
         interestRate = rate;
     }
-    @Override
-    public void withdraw(double amount) {
-        if (amount + 5.0 &gt; balance) {
-            System.out.println("Cannot withdraw");
-        } else {
-            balance -= (amount + 5.0);
-        }
-    }
 }
 public class TestBank {
     public static void main(String[] args) {
-        Account acc = new SavingAccount("SA001", 1000.0, 0.05);
-        try {
-            acc.withdraw(200.0);
-            acc.printInfo();
-        } catch (Exception e) {
-            System.out.println(e.getMessage());
-        }
+        Account acc1 = new Account("ACC01", 500.0);
+        Account acc2 = new SavingAccount("SA001", 1000.0, 0.05);
+        acc2.deposit(200.0);
+        acc2.printInfo();
     }
 }</t>
         </is>
@@ -2513,7 +2299,8 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chương trình Java trên có lỗi biên dịch nào? Hãy chỉ ra câu lệnh gây lỗi, giải thích nguyên nhân và đưa ra phương án sửa để chương trình biên dịch thành công.</t>
+          <t>Chương trình Java trên có chứa các lỗi biên dịch. Hãy chỉ ra các câu lệnh gây lỗi, giải thích nguyên nhân và đưa ra phương án sửa để chương trình biên dịch thành công.
+(Quy định chấm: Thí sinh chỉ cần chỉ ra VÀ SỬA ĐÚNG ít nhất 3 lỗi sai sẽ đạt điểm tối đa 1.0 điểm. Nếu chỉ phát hiện đúng lỗi mà không đưa ra phương án sửa hợp lệ thì chỉ nhận 50% số điểm của lỗi đó - 0.167 điểm/lỗi).</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2524,21 +2311,27 @@
           <t>llm_assisted</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Lỗi biên dịch:
-Constructor SavingAccount(String accNum, double initialBalance, double rate) không gọi super(...) tường minh, nên Java tự động gọi super() không tham số, nhưng lớp Account không có constructor không tham số.
-Sửa lỗi: Thêm super(accNum, initialBalance); ở dòng đầu tiên của constructor SavingAccount.</t>
+          <t>Danh sách 5 lỗi biên dịch:
+1. Từ khóa Public ở phương thức Public void deposit(...) trong Account viết hoa chữ P (lỗi cú pháp Java, phải viết thường public).
+2. In SavingAccount(double rate), lời gọi super(...) nằm sau câu lệnh interestRate = rate; (lời gọi super(...) bắt buộc phải là câu lệnh đầu tiên trong constructor).
+3. SavingAccount(String, double, double) không gọi super(...) tường minh, ngầm gọi super() không tham số nhưng Account không có constructor mặc định không tham số.
+4. Lớp SavingAccount kế thừa abstract class Account nhưng không override phương thức trừu tượng processMonthlyFee().
+5. In main: Account acc1 = new Account("ACC01", 500.0); khởi tạo trực tiếp đối tượng từ abstract class Account.
+Quy định chấm điểm cho Câu 4.a (tổng điểm tối đa 1.0):
+- Sinh viên tìm và sửa đúng 1 lỗi: 0.333 điểm (nếu chỉ tìm đúng lỗi mà không sửa / sửa sai: 0.167 điểm).
+- Sinh viên tìm và sửa đúng 2 lỗi: 0.667 điểm (nếu chỉ tìm đúng lỗi mà không sửa / sửa sai: 0.333 điểm).
+- Sinh viên tìm và sửa đúng từ 3 lỗi trở lên: 1.0 điểm (đạt điểm tối đa).
+- Mỗi lỗi nếu chỉ chỉ ra đúng mà không đưa ra phương án sửa hợp lệ: chỉ tính 50% số điểm của lỗi đó.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Đối chiếu tính chính xác khi chỉ ra lỗi thiếu super(...) trong constructor lớp con và phương án sửa hợp lệ.</t>
+          <t>Chấm bài tự động/LLM cho câu 4.a theo quy định:
+1. Đoạn mã chứa 5 lỗi biên dịch tiềm năng.
+2. Mỗi lỗi sinh viên chỉ ra VÀ SỬA ĐÚNG được cộng 0.333 điểm. Nếu sinh viên chỉ phát hiện đúng dòng lỗi/nguyên nhân mà KHÔNG SỬA được hoặc SỬA SAI thì chỉ tính 50% điểm của lỗi đó (0.167 điểm/lỗi).
+3. Tổng điểm C4.a = Min(1.0, Tổng điểm các lỗi đạt được). Sinh viên chỉ cần chỉ ra VÀ SỬA ĐÚNG từ 3 lỗi trở lên sẽ nhận điểm tối đa 1.0 điểm.</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2346,6 @@
           <t>Câu 4 - Đọc và sửa mã Java (1,5 điểm)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>C4.b</t>
@@ -2566,7 +2358,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sau khi sửa lỗi biên dịch ở câu 4.a (constructor SavingAccount gọi super(accNum, initialBalance) và gán interestRate = rate), câu lệnh acc.withdraw(200.0); và acc.printInfo(); trong hàm main sẽ in ra màn hình kết quả chính xác như thế nào? Giải thích quá trình thực thi.</t>
+          <t>Sau khi sửa các lỗi biên dịch ở câu 4.a, câu lệnh acc2.deposit(200.0); và acc2.printInfo(); trong hàm main sẽ in ra màn hình kết quả chính xác như thế nào? Giải thích quá trình thực thi.</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2577,15 +2369,10 @@
           <t>llm_assisted</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Kết quả in ra màn hình: Acc: SA001, Balance: 795.0
-Giải thích: acc trỏ tới đối tượng SavingAccount. Khi acc.withdraw(200.0) chạy, phương thức withdraw của SavingAccount được gọi (Dynamic binding), trừ 200.0 + 5.0 (phí) = 205.0, số dư còn 1000.0 - 205.0 = 795.0. acc.printInfo() in ra Acc: SA001, Balance: 795.0.</t>
+          <t>Kết quả in ra màn hình: Acc: SA001, Balance: 1200.0
+Giải thích: acc2 trỏ tới đối tượng SavingAccount. Lời gọi deposit(200.0) nạp thêm 200.0 vào balance (1000.0 + 200.0 = 1200.0). acc2.printInfo() in ra Acc: SA001, Balance: 1200.0.</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2628,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2742,84 +2529,103 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C4.a</t>
+          <t>C4.b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>missing-super-call</t>
+          <t>correct-output</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phát hiện chính xác lỗi constructor SavingAccount ngầm gọi super() mặc định không tồn tại ở Account</t>
+          <t>Xác định đúng chuỗi kết quả in ra màn hình: Acc: SA001, Balance: 795.0</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C4.a</t>
+          <t>C4.b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fix-super-call</t>
+          <t>execution-explanation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Đưa ra phương án sửa đúng: bổ sung super(accNum, initialBalance) ở dòng đầu tiên trong constructor SavingAccount</t>
+          <t>Giải thích đúng quá trình thực thi rút tiền kèm phí 5.0 và cơ chế liên kết động (Dynamic binding) khi gọi withdraw()</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C4.b</t>
+          <t>C4.a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>correct-output</t>
+          <t>error-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xác định đúng chuỗi kết quả in ra màn hình: Acc: SA001, Balance: 795.0</t>
+          <t>Chỉ ra và sửa đúng lỗi biên dịch thứ 1 (0.333đ; chỉ chỉ ra không sửa: 0.167đ)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C4.b</t>
+          <t>C4.a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>execution-explanation</t>
+          <t>error-2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Giải thích đúng quá trình thực thi rút tiền kèm phí 5.0 và cơ chế liên kết động (Dynamic binding) khi gọi withdraw()</t>
+          <t>Chỉ ra và sửa đúng lỗi biên dịch thứ 2 (0.333đ; chỉ chỉ ra không sửa: 0.167đ)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1"/>
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C4.a</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>error-3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chỉ ra và sửa đúng lỗi biên dịch thứ 3 (đạt điểm tối đa 1.0 điểm khi tìm &amp; sửa đúng &gt;= 3 lỗi)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.334</v>
+      </c>
+    </row>
     <row r="11" ht="42" customHeight="1"/>
     <row r="12" ht="42" customHeight="1"/>
   </sheetData>
